--- a/old/260608.xlsx
+++ b/old/260608.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tac3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED222E9-3AD4-4DDC-8454-AE57A8CA52F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0676CB4-D2F3-4FA9-9573-E180C10D7CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8420" yWindow="3820" windowWidth="16180" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10320" yWindow="3760" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId1"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,22 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>sonst gehen die nämlich zu Siemens</t>
-  </si>
-  <si>
-    <t>Hause nicht mehr</t>
-  </si>
-  <si>
-    <t>Es gibt aber andererseits</t>
-  </si>
-  <si>
-    <t>eng verzahnt</t>
-  </si>
-  <si>
-    <t>rahmensetzende Politik herantragen</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>allmählich ein Ende der chaotischen</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -377,59 +360,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0250B381-C0FF-4B3D-947F-291E0FCC1E74}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="40.9140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1430AC9D-76FD-4EE4-BF0C-AF97D8A2C7D0}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="33.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEAF128-F2BF-4235-B376-A175BAFDBF22}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -439,12 +369,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -453,7 +383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
